--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_247_R25.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_247_R25.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2449</v>
+        <v>5.2872</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9034</v>
+        <v>6.8784</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6585</v>
+        <v>-1.5913</v>
       </c>
       <c r="G2" t="n">
         <v>3.8881</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.0348</v>
+        <v>-0.9926</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1123</v>
+        <v>-0.1373</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9225</v>
+        <v>-0.8552999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>0.5361</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. DIALLO</t>
+          <t>M. JAMES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4323</v>
+        <v>2.8184</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1011</v>
+        <v>2.9599</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3311</v>
+        <v>-0.1415</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.1953</v>
+        <v>2.7064</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5149</v>
+        <v>2.4957</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.7103</v>
+        <v>0.2107</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9374</v>
+        <v>4.4398</v>
       </c>
       <c r="K3" t="n">
-        <v>0.612</v>
+        <v>2.9612</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.5493</v>
+        <v>1.4786</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.258</v>
+        <v>-1.7334</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.097</v>
+        <v>-0.4655</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.1609</v>
+        <v>-1.2679</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3195</v>
+        <v>2.7834</v>
       </c>
       <c r="S3" t="n">
-        <v>3.4678</v>
+        <v>-0.0993</v>
       </c>
       <c r="T3" t="n">
-        <v>3.126</v>
+        <v>0.02</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3418</v>
+        <v>-0.1193</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0.2525</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0722</v>
+        <v>0.8197</v>
       </c>
       <c r="X3" t="n">
         <v>-1.0722</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. JAMES</t>
+          <t>J. BLOSSOMGAME</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6679</v>
+        <v>0.4524</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9102</v>
+        <v>0.6172</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2423</v>
+        <v>-0.1647</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7064</v>
+        <v>-0.5504</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4957</v>
+        <v>0.2762</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2107</v>
+        <v>-0.8265</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4398</v>
+        <v>2.0516</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9612</v>
+        <v>0.8773</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4786</v>
+        <v>1.1742</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7334</v>
+        <v>-2.602</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4655</v>
+        <v>-0.6012</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2679</v>
+        <v>-2.0008</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7834</v>
+        <v>2.3195</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2498</v>
+        <v>-0.2987</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0297</v>
+        <v>-0.4165</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2201</v>
+        <v>0.1177</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2525</v>
+        <v>0.1418</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8197</v>
+        <v>0.1418</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. TARPEY</t>
+          <t>A. DIALLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0445</v>
+        <v>0.4152</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2052</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2498</v>
+        <v>0.3311</v>
       </c>
       <c r="G5" t="n">
-        <v>0.165</v>
+        <v>-2.1953</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.2905</v>
+        <v>0.5149</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4555</v>
+        <v>-2.7103</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3546</v>
+        <v>-0.9374</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.7863</v>
+        <v>0.612</v>
       </c>
       <c r="L5" t="n">
-        <v>1.141</v>
+        <v>-1.5493</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1896</v>
+        <v>-1.258</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5041</v>
+        <v>-0.097</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3145</v>
+        <v>-1.1609</v>
       </c>
       <c r="P5" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>0.232</v>
+        <v>2.3195</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4415</v>
+        <v>1.4508</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1494</v>
+        <v>1.109</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2921</v>
+        <v>0.3418</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. BLOSSOMGAME</t>
+          <t>T. TARPEY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2285</v>
+        <v>0.225</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0707</v>
+        <v>0.4411</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2991</v>
+        <v>-0.2162</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5504</v>
+        <v>0.165</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2762</v>
+        <v>-1.2905</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8265</v>
+        <v>1.4555</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0516</v>
+        <v>0.3546</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8773</v>
+        <v>-0.7863</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1742</v>
+        <v>1.141</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.602</v>
+        <v>-0.1896</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6012</v>
+        <v>-0.5041</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.0008</v>
+        <v>0.3145</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3195</v>
+        <v>0.232</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9796</v>
+        <v>-0.172</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.963</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0167</v>
+        <v>-0.2585</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. THEIS</t>
+          <t>E. OKOBO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5656</v>
+        <v>-1.1689</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.459</v>
+        <v>-0.7108</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1065</v>
+        <v>-0.4581</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.1339</v>
+        <v>-0.6696</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3434</v>
+        <v>-2.0347</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.7905</v>
+        <v>1.365</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.7079</v>
+        <v>1.514</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3929</v>
+        <v>-1.9053</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3151</v>
+        <v>3.4193</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.426</v>
+        <v>-2.1837</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0495</v>
+        <v>-0.1294</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.4755</v>
+        <v>-2.0543</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R7" t="n">
         <v>1.8556</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1946</v>
+        <v>-0.0354</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0193</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2139</v>
+        <v>-0.13</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.428</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. HAYES</t>
+          <t>D. THEIS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9644</v>
+        <v>-1.4663</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4449</v>
+        <v>-0.1917</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5195</v>
+        <v>-1.2746</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2138</v>
+        <v>-3.1339</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.9567</v>
+        <v>-0.3434</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7429</v>
+        <v>-2.7905</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5487</v>
+        <v>-1.7079</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7695</v>
+        <v>-0.3929</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2208</v>
+        <v>-1.3151</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6651</v>
+        <v>-1.426</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1871</v>
+        <v>0.0495</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5221</v>
+        <v>-1.4755</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3216</v>
+        <v>0.2939</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2636</v>
+        <v>0.248</v>
       </c>
       <c r="U8" t="n">
-        <v>0.058</v>
+        <v>0.0459</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0722</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.428</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0722</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1291</v>
+        <v>-1.708</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5465</v>
+        <v>-1.1927</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5826</v>
+        <v>-0.5154</v>
       </c>
       <c r="G9" t="n">
         <v>-1.8597</v>
@@ -1156,13 +1156,13 @@
         <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.339</v>
+        <v>-0.9179</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5975</v>
+        <v>-0.2436</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7415</v>
+        <v>-0.6743</v>
       </c>
       <c r="V9" t="n">
         <v>0.1418</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. OKOBO</t>
+          <t>K. HAYES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1439</v>
+        <v>-2.3273</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6858</v>
+        <v>-1.6061</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4581</v>
+        <v>-0.7212</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6696</v>
+        <v>-1.2138</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0347</v>
+        <v>-1.9567</v>
       </c>
       <c r="I10" t="n">
-        <v>1.365</v>
+        <v>0.7429</v>
       </c>
       <c r="J10" t="n">
-        <v>1.514</v>
+        <v>-0.5487</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.9053</v>
+        <v>-0.7695</v>
       </c>
       <c r="L10" t="n">
-        <v>3.4193</v>
+        <v>0.2208</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.1837</v>
+        <v>-0.6651</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1294</v>
+        <v>-1.1871</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.0543</v>
+        <v>0.5221</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0104</v>
+        <v>-0.0413</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8804</v>
+        <v>0.1024</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.13</v>
+        <v>-0.1436</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8999</v>
+        <v>-4.0384</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7133</v>
+        <v>-2.8182</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1866</v>
+        <v>-1.2202</v>
       </c>
       <c r="G11" t="n">
         <v>-3.0021</v>
@@ -1312,13 +1312,13 @@
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8702</v>
+        <v>-0.2682</v>
       </c>
       <c r="T11" t="n">
-        <v>1.4629</v>
+        <v>0.358</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5926</v>
+        <v>-0.6262</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5361</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6308</v>
+        <v>-1.5107</v>
       </c>
       <c r="E12" t="n">
-        <v>3.341099999999999</v>
+        <v>4.461200000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.9719</v>
+        <v>-5.972099999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.865300000000001</v>
+        <v>-5.8653</v>
       </c>
       <c r="H12" t="n">
         <v>-7.454499999999999</v>
@@ -1363,10 +1363,10 @@
         <v>1.5891</v>
       </c>
       <c r="J12" t="n">
-        <v>7.324299999999998</v>
+        <v>7.324300000000002</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.8717999999999997</v>
+        <v>-0.8718000000000002</v>
       </c>
       <c r="L12" t="n">
         <v>8.196300000000001</v>
@@ -1381,7 +1381,7 @@
         <v>-6.6073</v>
       </c>
       <c r="P12" t="n">
-        <v>5.7989</v>
+        <v>5.798899999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>-10.438</v>
@@ -1390,16 +1390,16 @@
         <v>16.2366</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.2009</v>
+        <v>-1.0807</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1009</v>
+        <v>1.2212</v>
       </c>
       <c r="U12" t="n">
         <v>-2.3018</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3632</v>
+        <v>-0.3632000000000002</v>
       </c>
       <c r="W12" t="n">
         <v>6.3536</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>N. AKELE</t>
+          <t>L. VILDOZA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.6126</v>
+        <v>4.3815</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1603</v>
+        <v>3.4391</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4522</v>
+        <v>0.9423</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5109</v>
+        <v>2.3345</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9014</v>
+        <v>2.204</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6095</v>
+        <v>0.1305</v>
       </c>
       <c r="J13" t="n">
-        <v>3.6436</v>
+        <v>2.302</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6624</v>
+        <v>1.4823</v>
       </c>
       <c r="L13" t="n">
-        <v>2.9812</v>
+        <v>0.8196</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.1326</v>
+        <v>0.0325</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2391</v>
+        <v>0.7217</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.3717</v>
+        <v>-0.6891</v>
       </c>
       <c r="P13" t="n">
-        <v>0.4639</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1598</v>
+        <v>-2.5515</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S13" t="n">
-        <v>1.6377</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6765</v>
+        <v>0.472</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9612000000000001</v>
+        <v>0.2139</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>3.2166</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.2166</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L. VILDOZA</t>
+          <t>D. ALSTON JR.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3764</v>
+        <v>3.65</v>
       </c>
       <c r="E14" t="n">
-        <v>3.793</v>
+        <v>4.0251</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5834</v>
+        <v>-0.3751</v>
       </c>
       <c r="G14" t="n">
-        <v>2.3345</v>
+        <v>4.455</v>
       </c>
       <c r="H14" t="n">
-        <v>2.204</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1305</v>
+        <v>3.8345</v>
       </c>
       <c r="J14" t="n">
-        <v>2.302</v>
+        <v>5.2304</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4823</v>
+        <v>0.864</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8196</v>
+        <v>4.3664</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0325</v>
+        <v>-0.7754</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7217</v>
+        <v>-0.2435</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6891</v>
+        <v>-0.5319</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.8556</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.5515</v>
+        <v>-1.3917</v>
       </c>
       <c r="R14" t="n">
         <v>0.6959</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6808999999999999</v>
+        <v>-0.1092</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8259</v>
+        <v>-0.3497</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.145</v>
+        <v>0.2405</v>
       </c>
       <c r="V14" t="n">
-        <v>3.2166</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.2166</v>
+        <v>0.5361</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. ALSTON JR.</t>
+          <t>N. AKELE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9645</v>
+        <v>3.6195</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5533</v>
+        <v>2.5706</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5888</v>
+        <v>1.0489</v>
       </c>
       <c r="G15" t="n">
-        <v>4.455</v>
+        <v>2.5109</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.9014</v>
       </c>
       <c r="I15" t="n">
-        <v>3.8345</v>
+        <v>1.6095</v>
       </c>
       <c r="J15" t="n">
-        <v>5.2304</v>
+        <v>3.6436</v>
       </c>
       <c r="K15" t="n">
-        <v>0.864</v>
+        <v>0.6624</v>
       </c>
       <c r="L15" t="n">
-        <v>4.3664</v>
+        <v>2.9812</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7754</v>
+        <v>-1.1326</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2435</v>
+        <v>0.2391</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5319</v>
+        <v>-1.3717</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7947</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8215</v>
+        <v>0.0868</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0268</v>
+        <v>0.5579</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4856</v>
+        <v>1.979</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8913</v>
+        <v>2.8349</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4057</v>
+        <v>-0.8559</v>
       </c>
       <c r="G16" t="n">
         <v>1.1926</v>
@@ -1702,13 +1702,13 @@
         <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5652</v>
+        <v>-0.0718</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7468</v>
+        <v>0.1968</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8184</v>
+        <v>-0.2686</v>
       </c>
       <c r="V16" t="n">
         <v>0.3943</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4182</v>
+        <v>0.3573</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8542</v>
+        <v>-0.7363</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2724</v>
+        <v>1.0936</v>
       </c>
       <c r="G17" t="n">
         <v>0.1226</v>
@@ -1780,13 +1780,13 @@
         <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7389</v>
+        <v>0.6781</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2636</v>
+        <v>0.3815</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4753</v>
+        <v>0.2965</v>
       </c>
       <c r="V17" t="n">
         <v>0.2525</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. DIARRA</t>
+          <t>S. NIANG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0187</v>
+        <v>-0.3131</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1436</v>
+        <v>1.6898</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1249</v>
+        <v>-2.0029</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7173</v>
+        <v>0.1401</v>
       </c>
       <c r="H18" t="n">
-        <v>2.5737</v>
+        <v>0.0396</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8564000000000001</v>
+        <v>0.1005</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3354</v>
+        <v>0.8404</v>
       </c>
       <c r="K18" t="n">
-        <v>2.1881</v>
+        <v>0.1043</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1472</v>
+        <v>0.7361</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6181</v>
+        <v>-0.7003</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3856</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0037</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.0876</v>
+        <v>0.4639</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.5515</v>
+        <v>-0.232</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>1.7137</v>
+        <v>1.1165</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6122</v>
+        <v>1.0813</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1015</v>
+        <v>0.0351</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.3247</v>
+        <v>-2.0336</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.2525</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0722</v>
+        <v>-2.0336</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. NIANG</t>
+          <t>A. DIARRA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5097</v>
+        <v>-0.9864000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8078</v>
+        <v>0.082</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.3175</v>
+        <v>-1.0685</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1401</v>
+        <v>1.7173</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0396</v>
+        <v>2.5737</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1005</v>
+        <v>-0.8564000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8404</v>
+        <v>2.3354</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1043</v>
+        <v>2.1881</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7361</v>
+        <v>0.1472</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7003</v>
+        <v>-0.6181</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.06469999999999999</v>
+        <v>0.3856</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-1.0037</v>
       </c>
       <c r="P19" t="n">
+        <v>-2.0876</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-2.5515</v>
+      </c>
+      <c r="R19" t="n">
         <v>0.4639</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-0.232</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.6959</v>
-      </c>
       <c r="S19" t="n">
-        <v>0.9199000000000001</v>
+        <v>0.7086</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1993</v>
+        <v>0.5507</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2794</v>
+        <v>0.1579</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.0336</v>
+        <v>-1.3247</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.2525</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.0336</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. FERRARI</t>
+          <t>M. ACCORSI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5989</v>
+        <v>-1.5311</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7906</v>
+        <v>-1.4801</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8083</v>
+        <v>-0.051</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.9881</v>
+        <v>-1.5665</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1344</v>
+        <v>0.5114</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.8537</v>
+        <v>-2.0779</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7159</v>
+        <v>-1.4487</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0336</v>
+        <v>0.0504</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-1.4991</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2722</v>
+        <v>-0.1178</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.168</v>
+        <v>0.461</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1041</v>
+        <v>-0.5788</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0747</v>
+        <v>0.0354</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0747</v>
+        <v>-0.0314</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>0.0668</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. ACCORSI</t>
+          <t>F. FERRARI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7835</v>
+        <v>-1.5989</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.598</v>
+        <v>-0.7906</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1855</v>
+        <v>-0.8083</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5665</v>
+        <v>-1.9881</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5114</v>
+        <v>-0.1344</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.0779</v>
+        <v>-1.8537</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.4487</v>
+        <v>-0.7159</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0504</v>
+        <v>0.0336</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.4991</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1178</v>
+        <v>-1.2722</v>
       </c>
       <c r="N21" t="n">
-        <v>0.461</v>
+        <v>-0.168</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5788</v>
+        <v>-1.1041</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.217</v>
+        <v>-0.0747</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1494</v>
+        <v>-0.0747</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0677</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5379</v>
+        <v>-1.7629</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7567</v>
+        <v>-2.049</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2188</v>
+        <v>0.286</v>
       </c>
       <c r="G22" t="n">
         <v>-3.572</v>
@@ -2170,13 +2170,13 @@
         <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5921999999999999</v>
+        <v>0.1828</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7468</v>
+        <v>-0.0391</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1546</v>
+        <v>0.2219</v>
       </c>
       <c r="V22" t="n">
         <v>0.9304</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8151</v>
+        <v>-3.5913</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3778</v>
+        <v>-3.6137</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4373</v>
+        <v>0.0224</v>
       </c>
       <c r="G23" t="n">
         <v>0.5189</v>
@@ -2248,13 +2248,13 @@
         <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2464</v>
+        <v>-0.0226</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2636</v>
+        <v>0.0277</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.51</v>
+        <v>-0.0503</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0722</v>
@@ -2281,34 +2281,34 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>2.6309</v>
+        <v>4.203599999999998</v>
       </c>
       <c r="E24" t="n">
-        <v>5.971999999999998</v>
+        <v>5.971800000000002</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.3412</v>
+        <v>-1.7685</v>
       </c>
       <c r="G24" t="n">
-        <v>5.8653</v>
+        <v>5.865300000000002</v>
       </c>
       <c r="H24" t="n">
         <v>7.454300000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.5889</v>
+        <v>-1.588900000000001</v>
       </c>
       <c r="J24" t="n">
         <v>13.1899</v>
       </c>
       <c r="K24" t="n">
-        <v>6.582399999999999</v>
+        <v>6.582400000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>6.607299999999999</v>
+        <v>6.607300000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-7.3244</v>
+        <v>-7.324399999999999</v>
       </c>
       <c r="N24" t="n">
         <v>0.8720999999999999</v>
@@ -2326,13 +2326,13 @@
         <v>10.4381</v>
       </c>
       <c r="S24" t="n">
-        <v>2.2009</v>
+        <v>3.7738</v>
       </c>
       <c r="T24" t="n">
         <v>2.3019</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1011</v>
+        <v>1.4716</v>
       </c>
       <c r="V24" t="n">
         <v>0.3633000000000002</v>
